--- a/2026 NU health comparison - INDIVIDUAL.xlsx
+++ b/2026 NU health comparison - INDIVIDUAL.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d28b3282b7dd9da/Transfer/Kellogg Master/Benefits/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pbh634\Documents\GitHub\nu-health-plan-comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="207" documentId="13_ncr:1_{77191DF6-FCC8-4D80-BE69-90045571E4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9DEC2972-92CA-4AB0-B7AB-54F4BCE64F7D}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF0ECCA-6F4A-462B-B8D5-62CAE0FB5929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
     <author>Paul Hively</author>
   </authors>
   <commentList>
-    <comment ref="A4" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
@@ -68,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
@@ -92,7 +92,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="A7" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
@@ -116,7 +116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A10" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="A11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
@@ -140,7 +140,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A11" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
+    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000005000000}">
       <text>
         <r>
           <rPr>
@@ -164,7 +164,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A12" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
+    <comment ref="A13" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000006000000}">
       <text>
         <r>
           <rPr>
@@ -193,12 +193,9 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="173" uniqueCount="54">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="55">
   <si>
     <t>HMO</t>
-  </si>
-  <si>
-    <t>Premium</t>
   </si>
   <si>
     <t>Comparison</t>
@@ -358,6 +355,12 @@
   </si>
   <si>
     <t>VPPO-&gt;HSAe</t>
+  </si>
+  <si>
+    <t>Monthly premium</t>
+  </si>
+  <si>
+    <t>Monthly HSA</t>
   </si>
 </sst>
 </file>
@@ -561,6 +564,78 @@
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
+    </dxf>
+    <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
@@ -571,78 +646,6 @@
     </dxf>
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="164" formatCode="&quot;$&quot;#,##0"/>
@@ -957,7 +960,7 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Calculator!$B$9</c:f>
+              <c:f>Calculator!$B$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -992,7 +995,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Calculator!$A$10:$A$12</c:f>
+              <c:f>Calculator!$A$11:$A$13</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1009,7 +1012,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Calculator!$B$10:$B$12</c:f>
+              <c:f>Calculator!$B$11:$B$13</c:f>
               <c:numCache>
                 <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1037,7 +1040,7 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Calculator!$C$9</c:f>
+              <c:f>Calculator!$C$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1072,7 +1075,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Calculator!$A$10:$A$12</c:f>
+              <c:f>Calculator!$A$11:$A$13</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1089,7 +1092,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Calculator!$C$10:$C$12</c:f>
+              <c:f>Calculator!$C$11:$C$13</c:f>
               <c:numCache>
                 <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1117,7 +1120,7 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Calculator!$D$9</c:f>
+              <c:f>Calculator!$D$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1152,7 +1155,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Calculator!$A$10:$A$12</c:f>
+              <c:f>Calculator!$A$11:$A$13</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1169,7 +1172,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Calculator!$D$10:$D$12</c:f>
+              <c:f>Calculator!$D$11:$D$13</c:f>
               <c:numCache>
                 <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
                 <c:ptCount val="3"/>
@@ -1197,7 +1200,7 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Calculator!$E$9</c:f>
+              <c:f>Calculator!$E$10</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
@@ -1232,7 +1235,7 @@
           </c:marker>
           <c:cat>
             <c:strRef>
-              <c:f>Calculator!$A$10:$A$12</c:f>
+              <c:f>Calculator!$A$11:$A$13</c:f>
               <c:strCache>
                 <c:ptCount val="3"/>
                 <c:pt idx="0">
@@ -1249,7 +1252,7 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Calculator!$E$10:$E$12</c:f>
+              <c:f>Calculator!$E$11:$E$13</c:f>
               <c:numCache>
                 <c:formatCode>"$"#,##0_);[Red]\("$"#,##0\)</c:formatCode>
                 <c:ptCount val="3"/>
@@ -2017,14 +2020,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>5953</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
       <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:row>34</xdr:row>
+      <xdr:rowOff>82153</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2055,8 +2058,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:E14">
-  <autoFilter ref="A1:E14" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:E15">
+  <autoFilter ref="A1:E15" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Comparison" totalsRowLabel="Total"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="PPO" dataDxfId="65" totalsRowDxfId="64"/>
@@ -2073,10 +2076,10 @@
   <autoFilter ref="B54:F59" xr:uid="{7ED47D39-3E05-484F-ACD6-DE3122FA858C}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{CC8D7EE5-FC07-4A78-8C74-AB114F5DC103}" name="Salary tier"/>
-    <tableColumn id="2" xr3:uid="{8D495E23-05A1-42D6-A30C-50F38F65495F}" name="PPPO" dataDxfId="27"/>
-    <tableColumn id="3" xr3:uid="{8C99191F-99A5-42CB-845E-07207FEB5423}" name="SPPO" dataDxfId="26"/>
-    <tableColumn id="4" xr3:uid="{7C6A2569-5707-4A10-AB7A-A2BFEDC34DC4}" name="VPPO" dataDxfId="25"/>
-    <tableColumn id="5" xr3:uid="{87A1F397-88B8-45AB-9A60-D4FB1E9169F9}" name="HMO" dataDxfId="24"/>
+    <tableColumn id="2" xr3:uid="{8D495E23-05A1-42D6-A30C-50F38F65495F}" name="PPPO" dataDxfId="23"/>
+    <tableColumn id="3" xr3:uid="{8C99191F-99A5-42CB-845E-07207FEB5423}" name="SPPO" dataDxfId="22"/>
+    <tableColumn id="4" xr3:uid="{7C6A2569-5707-4A10-AB7A-A2BFEDC34DC4}" name="VPPO" dataDxfId="21"/>
+    <tableColumn id="5" xr3:uid="{87A1F397-88B8-45AB-9A60-D4FB1E9169F9}" name="HMO" dataDxfId="20"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2087,10 +2090,10 @@
   <autoFilter ref="B74:F79" xr:uid="{D0E08A80-DCF9-4150-81F6-042774F44EB2}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{6FBC44EB-3779-486C-B622-C894BD4EC01D}" name="Salary tier"/>
-    <tableColumn id="2" xr3:uid="{32675F21-9B3C-486B-BEAA-1DAA5127E34B}" name="PPPO" dataDxfId="23"/>
-    <tableColumn id="3" xr3:uid="{7649762A-2E37-4A48-8704-FB5140E2C666}" name="SPPO" dataDxfId="22"/>
-    <tableColumn id="4" xr3:uid="{494FBE12-A051-4FD9-B65B-C36AE6745CE0}" name="VPPO" dataDxfId="21"/>
-    <tableColumn id="5" xr3:uid="{14A5E1F3-FCD5-4916-8DFF-4B53582F744B}" name="HMO" dataDxfId="20"/>
+    <tableColumn id="2" xr3:uid="{32675F21-9B3C-486B-BEAA-1DAA5127E34B}" name="PPPO" dataDxfId="19"/>
+    <tableColumn id="3" xr3:uid="{7649762A-2E37-4A48-8704-FB5140E2C666}" name="SPPO" dataDxfId="18"/>
+    <tableColumn id="4" xr3:uid="{494FBE12-A051-4FD9-B65B-C36AE6745CE0}" name="VPPO" dataDxfId="17"/>
+    <tableColumn id="5" xr3:uid="{14A5E1F3-FCD5-4916-8DFF-4B53582F744B}" name="HMO" dataDxfId="16"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2101,10 +2104,10 @@
   <autoFilter ref="B84:F89" xr:uid="{7FCE7F7E-C181-4430-A243-A452806DDE7C}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{10E9A5E7-EB37-4577-B6B3-9F802BE0D8E8}" name="Salary tier"/>
-    <tableColumn id="2" xr3:uid="{2270EE98-19A7-4EC5-A5DA-D3E97BB1B06C}" name="PPPO" dataDxfId="19"/>
-    <tableColumn id="3" xr3:uid="{FD3D919D-0492-40B6-8FD3-EDF5C1672490}" name="SPPO" dataDxfId="18"/>
-    <tableColumn id="4" xr3:uid="{BE0151A0-4EE2-4430-BF5B-2ECAE11A931E}" name="VPPO" dataDxfId="17"/>
-    <tableColumn id="5" xr3:uid="{05FA8952-4A1E-4D91-B2C0-8EEF64D74426}" name="HMO" dataDxfId="16"/>
+    <tableColumn id="2" xr3:uid="{2270EE98-19A7-4EC5-A5DA-D3E97BB1B06C}" name="PPPO" dataDxfId="15"/>
+    <tableColumn id="3" xr3:uid="{FD3D919D-0492-40B6-8FD3-EDF5C1672490}" name="SPPO" dataDxfId="14"/>
+    <tableColumn id="4" xr3:uid="{BE0151A0-4EE2-4430-BF5B-2ECAE11A931E}" name="VPPO" dataDxfId="13"/>
+    <tableColumn id="5" xr3:uid="{05FA8952-4A1E-4D91-B2C0-8EEF64D74426}" name="HMO" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2115,10 +2118,10 @@
   <autoFilter ref="B24:F29" xr:uid="{AF2455AA-F858-4745-8404-A94BB6DF8D32}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{E3DA2936-4D4C-45DB-B8F7-BD2DAA415386}" name="Salary tier"/>
-    <tableColumn id="2" xr3:uid="{32903C48-FB01-4495-A1E3-ABFDC39FD89B}" name="PPPO" dataDxfId="15"/>
-    <tableColumn id="3" xr3:uid="{70D7641D-C6E6-4299-8A68-DA1E023631D9}" name="SPPO" dataDxfId="14"/>
-    <tableColumn id="4" xr3:uid="{D0978A87-9C43-44F1-B443-B8C2AD731A28}" name="VPPO" dataDxfId="13"/>
-    <tableColumn id="5" xr3:uid="{3F0536A4-6BD9-4F95-BE01-C4B5F49B44EE}" name="HMO" dataDxfId="12"/>
+    <tableColumn id="2" xr3:uid="{32903C48-FB01-4495-A1E3-ABFDC39FD89B}" name="PPPO" dataDxfId="11"/>
+    <tableColumn id="3" xr3:uid="{70D7641D-C6E6-4299-8A68-DA1E023631D9}" name="SPPO" dataDxfId="10"/>
+    <tableColumn id="4" xr3:uid="{D0978A87-9C43-44F1-B443-B8C2AD731A28}" name="VPPO" dataDxfId="9"/>
+    <tableColumn id="5" xr3:uid="{3F0536A4-6BD9-4F95-BE01-C4B5F49B44EE}" name="HMO" dataDxfId="8"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2129,10 +2132,10 @@
   <autoFilter ref="B14:F19" xr:uid="{797B194A-6F04-4EC5-B972-C533C2EB2F62}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{534B5E41-7C6E-413A-A453-F25CCDEEBA85}" name="Salary tier"/>
-    <tableColumn id="2" xr3:uid="{FE1F2B92-1B50-442C-93DE-403B0DCD374B}" name="PPO" dataDxfId="11"/>
-    <tableColumn id="3" xr3:uid="{7477DF3B-9561-4CBE-9E44-1F83F00AF87C}" name="HSA+" dataDxfId="10"/>
-    <tableColumn id="4" xr3:uid="{F881019D-CADF-43C9-A7E4-50AAB24B37E0}" name="HSAe" dataDxfId="9"/>
-    <tableColumn id="5" xr3:uid="{0E93F931-3FB8-452A-AB35-68B61E76A840}" name="HMO" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{FE1F2B92-1B50-442C-93DE-403B0DCD374B}" name="PPO" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{7477DF3B-9561-4CBE-9E44-1F83F00AF87C}" name="HSA+" dataDxfId="6"/>
+    <tableColumn id="4" xr3:uid="{F881019D-CADF-43C9-A7E4-50AAB24B37E0}" name="HSAe" dataDxfId="5"/>
+    <tableColumn id="5" xr3:uid="{0E93F931-3FB8-452A-AB35-68B61E76A840}" name="HMO" dataDxfId="4"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2143,16 +2146,16 @@
   <autoFilter ref="I24:M29" xr:uid="{0DE184C8-FF89-42C1-87CF-BF51FF85BFBA}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{1420C700-5FB8-4802-82CF-FB33F7EF5C3A}" name="Salary tier"/>
-    <tableColumn id="2" xr3:uid="{F43CDEAC-D1B6-4CD3-8871-4B52C0CCB6F3}" name="PPPO" dataDxfId="4" dataCellStyle="Percent">
+    <tableColumn id="2" xr3:uid="{F43CDEAC-D1B6-4CD3-8871-4B52C0CCB6F3}" name="PPPO" dataDxfId="3" dataCellStyle="Percent">
       <calculatedColumnFormula>VLOOKUP(Year1&amp;$A5,$A$10:$F$1019,COLUMN(C$4),0)/VLOOKUP(Year2&amp;$A5,$A$10:$F$1019,COLUMN(C$4),0)-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{35128940-0E49-4374-8EF8-4044E1BB9B45}" name="SPPO" dataDxfId="7">
+    <tableColumn id="3" xr3:uid="{35128940-0E49-4374-8EF8-4044E1BB9B45}" name="SPPO" dataDxfId="2">
       <calculatedColumnFormula>VLOOKUP(Year1&amp;$A5,$A$10:$F$1019,COLUMN(D$4),0)/VLOOKUP(Year2&amp;$A5,$A$10:$F$1019,COLUMN(D$4),0)-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{C0A0BA70-F8E9-466B-8495-9A12A151227B}" name="VPPO" dataDxfId="6">
+    <tableColumn id="4" xr3:uid="{C0A0BA70-F8E9-466B-8495-9A12A151227B}" name="VPPO" dataDxfId="1">
       <calculatedColumnFormula>VLOOKUP(Year1&amp;$A5,$A$10:$F$1019,COLUMN(E$4),0)/VLOOKUP(Year2&amp;$A5,$A$10:$F$1019,COLUMN(E$4),0)-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{F067C46B-2E09-4FAD-A214-81E867B5873B}" name="HMO" dataDxfId="5">
+    <tableColumn id="5" xr3:uid="{F067C46B-2E09-4FAD-A214-81E867B5873B}" name="HMO" dataDxfId="0">
       <calculatedColumnFormula>VLOOKUP(Year1&amp;$A5,$A$10:$F$1019,COLUMN(F$4),0)/VLOOKUP(Year2&amp;$A5,$A$10:$F$1019,COLUMN(F$4),0)-1</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2250,16 +2253,16 @@
   <autoFilter ref="B4:F9" xr:uid="{D5EAF9D6-A011-4B56-A0D7-CFBDA22B0CA8}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{C5BAD141-A771-4C91-8283-9DCA0BC1CD6C}" name="Salary tier"/>
-    <tableColumn id="2" xr3:uid="{E2F452EA-9B4E-455B-8E7C-85A3B371B14E}" name="SPPO -&gt; PPO" dataDxfId="3" dataCellStyle="Percent">
+    <tableColumn id="2" xr3:uid="{E2F452EA-9B4E-455B-8E7C-85A3B371B14E}" name="SPPO -&gt; PPO" dataDxfId="31" dataCellStyle="Percent">
       <calculatedColumnFormula>C15/D25-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="3" xr3:uid="{1A68EE9A-B3CD-4D81-A854-D4CC0EA97A1F}" name="VPPO-&gt;HSA+" dataDxfId="2">
+    <tableColumn id="3" xr3:uid="{1A68EE9A-B3CD-4D81-A854-D4CC0EA97A1F}" name="VPPO-&gt;HSA+" dataDxfId="30">
       <calculatedColumnFormula>D15/E25-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="4" xr3:uid="{CDE95AE4-CFB7-4A93-8B1F-15D8E001FC05}" name="VPPO-&gt;HSAe" dataDxfId="0">
+    <tableColumn id="4" xr3:uid="{CDE95AE4-CFB7-4A93-8B1F-15D8E001FC05}" name="VPPO-&gt;HSAe" dataDxfId="29">
       <calculatedColumnFormula>E15/E25-1</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="5" xr3:uid="{601FA0AE-D606-4A72-B5FA-34F052E1BDB5}" name="HMO-&gt;HMO" dataDxfId="1">
+    <tableColumn id="5" xr3:uid="{601FA0AE-D606-4A72-B5FA-34F052E1BDB5}" name="HMO-&gt;HMO" dataDxfId="28">
       <calculatedColumnFormula>F15/F25-1</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -2272,10 +2275,10 @@
   <autoFilter ref="B64:F69" xr:uid="{13BF44A9-E241-44E6-99CC-85C7A0B3DD83}"/>
   <tableColumns count="5">
     <tableColumn id="1" xr3:uid="{BF40F38F-E121-4DB7-B73F-089B69B34354}" name="Salary tier"/>
-    <tableColumn id="2" xr3:uid="{B5EED1B4-5176-41FB-AF8C-E0B5535F9DA7}" name="PPPO" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{003616CD-F7D4-4714-A5FC-FD649AB63758}" name="SPPO" dataDxfId="30"/>
-    <tableColumn id="4" xr3:uid="{1886EBA3-963B-440B-8C53-106B4F005CF9}" name="VPPO" dataDxfId="29"/>
-    <tableColumn id="5" xr3:uid="{AA82DC92-04F2-4628-AB6E-A326B4F54D40}" name="HMO" dataDxfId="28"/>
+    <tableColumn id="2" xr3:uid="{B5EED1B4-5176-41FB-AF8C-E0B5535F9DA7}" name="PPPO" dataDxfId="27"/>
+    <tableColumn id="3" xr3:uid="{003616CD-F7D4-4714-A5FC-FD649AB63758}" name="SPPO" dataDxfId="26"/>
+    <tableColumn id="4" xr3:uid="{1886EBA3-963B-440B-8C53-106B4F005CF9}" name="VPPO" dataDxfId="25"/>
+    <tableColumn id="5" xr3:uid="{AA82DC92-04F2-4628-AB6E-A326B4F54D40}" name="HMO" dataDxfId="24"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -2544,7 +2547,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P18"/>
+  <dimension ref="A1:P19"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="22.140625" customWidth="1"/>
@@ -2559,40 +2562,40 @@
   <sheetData>
     <row r="1" spans="1:16" ht="30">
       <c r="A1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C1" t="s">
+        <v>50</v>
+      </c>
+      <c r="D1" t="s">
         <v>51</v>
-      </c>
-      <c r="D1" t="s">
-        <v>52</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="M1" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N1" t="s">
+        <v>50</v>
+      </c>
+      <c r="O1" t="s">
         <v>51</v>
-      </c>
-      <c r="O1" t="s">
-        <v>52</v>
       </c>
       <c r="P1" t="s">
         <v>0</v>
@@ -2600,7 +2603,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>53</v>
       </c>
       <c r="B2" s="3">
         <f>VLOOKUP($G$2,Table2[#All],COLUMN(),0)</f>
@@ -2619,16 +2622,16 @@
         <v>105</v>
       </c>
       <c r="G2" s="10" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H2" s="10" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="I2" s="14">
         <v>0.22</v>
       </c>
       <c r="L2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M2" s="1">
         <v>63</v>
@@ -2645,176 +2648,170 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" s="3">
+        <v>54</v>
+      </c>
+      <c r="B3" s="11"/>
+      <c r="C3" s="11">
+        <f>$G$6/12</f>
+        <v>83.333333333333329</v>
+      </c>
+      <c r="D3" s="11">
+        <f>$G$6/12</f>
+        <v>83.333333333333329</v>
+      </c>
+      <c r="E3" s="11"/>
+      <c r="L3" t="s">
+        <v>15</v>
+      </c>
+      <c r="M3" s="1">
+        <v>116</v>
+      </c>
+      <c r="N3" s="1">
+        <v>81</v>
+      </c>
+      <c r="O3" s="1">
+        <v>52</v>
+      </c>
+      <c r="P3" s="1">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="3">
         <f>B2*12</f>
         <v>1392</v>
       </c>
-      <c r="C3" s="3">
+      <c r="C4" s="3">
         <f>C2*12</f>
         <v>972</v>
       </c>
-      <c r="D3" s="3">
+      <c r="D4" s="3">
         <f>D2*12</f>
         <v>624</v>
       </c>
-      <c r="E3" s="3">
+      <c r="E4" s="3">
         <f>E2*12</f>
         <v>1260</v>
       </c>
-      <c r="L3" t="s">
-        <v>16</v>
-      </c>
-      <c r="M3" s="1">
-        <v>116</v>
-      </c>
-      <c r="N3" s="1">
-        <v>81</v>
-      </c>
-      <c r="O3" s="1">
-        <v>52</v>
-      </c>
-      <c r="P3" s="1">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16">
-      <c r="A4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B4" s="11">
-        <f>-1 * B3 * ($I$2 + 4.95%)</f>
+      <c r="G4" s="9" t="s">
+        <v>29</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="L4" t="s">
+        <v>32</v>
+      </c>
+      <c r="M4" s="1">
+        <v>197</v>
+      </c>
+      <c r="N4" s="1">
+        <v>148</v>
+      </c>
+      <c r="O4" s="1">
+        <v>117</v>
+      </c>
+      <c r="P4" s="1">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16">
+      <c r="A5" t="s">
+        <v>27</v>
+      </c>
+      <c r="B5" s="11">
+        <f>-1 * B4 * ($I$2 + 4.95%)</f>
         <v>-375.14400000000001</v>
       </c>
-      <c r="C4" s="11">
-        <f t="shared" ref="C4:E4" si="0">-1 * C3 * ($I$2 + 4.95%)</f>
+      <c r="C5" s="11">
+        <f t="shared" ref="C5:E5" si="0">-1 * C4 * ($I$2 + 4.95%)</f>
         <v>-261.95400000000001</v>
       </c>
-      <c r="D4" s="11">
+      <c r="D5" s="11">
         <f t="shared" si="0"/>
         <v>-168.16800000000001</v>
       </c>
-      <c r="E4" s="11">
+      <c r="E5" s="11">
         <f t="shared" si="0"/>
         <v>-339.57000000000005</v>
       </c>
-      <c r="G4" s="9" t="s">
+      <c r="G5" s="9" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="13" t="s">
-        <v>27</v>
-      </c>
-      <c r="L4" t="s">
-        <v>33</v>
-      </c>
-      <c r="M4" s="1">
-        <v>197</v>
-      </c>
-      <c r="N4" s="1">
-        <v>148</v>
-      </c>
-      <c r="O4" s="1">
-        <v>117</v>
-      </c>
-      <c r="P4" s="1">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16">
-      <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="B5" s="4"/>
-      <c r="C5" s="3">
+      <c r="I5" s="12">
+        <v>0.1</v>
+      </c>
+      <c r="L5" t="s">
+        <v>17</v>
+      </c>
+      <c r="M5" s="1">
+        <v>278</v>
+      </c>
+      <c r="N5" s="1">
+        <v>222</v>
+      </c>
+      <c r="O5" s="1">
+        <v>182</v>
+      </c>
+      <c r="P5" s="1">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16">
+      <c r="A6" t="s">
+        <v>2</v>
+      </c>
+      <c r="B6" s="4"/>
+      <c r="C6" s="3">
         <f>-1*MIN(G6, 1000)</f>
         <v>-1000</v>
       </c>
-      <c r="D5" s="3">
+      <c r="D6" s="3">
         <f>-1*MIN(G6, 1000)</f>
         <v>-1000</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="G5" s="9" t="s">
-        <v>31</v>
-      </c>
-      <c r="I5" s="12">
-        <v>0.1</v>
-      </c>
-      <c r="L5" t="s">
+      <c r="E6" s="4"/>
+      <c r="G6" s="16">
+        <v>1000</v>
+      </c>
+      <c r="I6" s="12">
+        <v>0.12</v>
+      </c>
+      <c r="L6" t="s">
         <v>18</v>
       </c>
-      <c r="M5" s="1">
-        <v>278</v>
-      </c>
-      <c r="N5" s="1">
-        <v>222</v>
-      </c>
-      <c r="O5" s="1">
-        <v>182</v>
-      </c>
-      <c r="P5" s="1">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16">
-      <c r="A6" t="s">
-        <v>29</v>
-      </c>
-      <c r="B6" s="7"/>
-      <c r="C6" s="11">
+      <c r="M6" s="1">
+        <v>434</v>
+      </c>
+      <c r="N6" s="1">
+        <v>345</v>
+      </c>
+      <c r="O6" s="1">
+        <v>292</v>
+      </c>
+      <c r="P6" s="1">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16">
+      <c r="A7" t="s">
+        <v>28</v>
+      </c>
+      <c r="B7" s="7"/>
+      <c r="C7" s="11">
         <f>-1 * G6 * ($I$2 + 4.95%)</f>
         <v>-269.5</v>
       </c>
-      <c r="D6" s="11">
+      <c r="D7" s="11">
         <f>-1 * G6 * ($I$2 + 4.95%)</f>
         <v>-269.5</v>
       </c>
-      <c r="E6" s="7"/>
-      <c r="G6" s="16">
-        <v>1000</v>
-      </c>
-      <c r="I6" s="12">
-        <v>0.12</v>
-      </c>
-      <c r="L6" t="s">
-        <v>19</v>
-      </c>
-      <c r="M6" s="1">
-        <v>434</v>
-      </c>
-      <c r="N6" s="1">
-        <v>345</v>
-      </c>
-      <c r="O6" s="1">
-        <v>292</v>
-      </c>
-      <c r="P6" s="1">
-        <v>393</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16">
-      <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="5">
-        <f>VLOOKUP($H$2,Table24[[#All],[Provider]:[HMO]],COLUMN(),0)</f>
-        <v>750</v>
-      </c>
-      <c r="C7" s="5">
-        <f>VLOOKUP($H$2,Table24[[#All],[Provider]:[HMO]],COLUMN(),0)</f>
-        <v>2000</v>
-      </c>
-      <c r="D7" s="5">
-        <f>VLOOKUP($H$2,Table24[[#All],[Provider]:[HMO]],COLUMN(),0)</f>
-        <v>4000</v>
-      </c>
-      <c r="E7" s="5">
-        <f>VLOOKUP($H$2,Table24[[#All],[Provider]:[HMO]],COLUMN(),0)</f>
-        <v>0</v>
-      </c>
+      <c r="E7" s="7"/>
       <c r="G7" s="2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="H7" s="17">
         <v>3400</v>
@@ -2828,113 +2825,113 @@
         <v>5</v>
       </c>
       <c r="B8" s="5">
+        <f>VLOOKUP($H$2,Table24[[#All],[Provider]:[HMO]],COLUMN(),0)</f>
+        <v>750</v>
+      </c>
+      <c r="C8" s="5">
+        <f>VLOOKUP($H$2,Table24[[#All],[Provider]:[HMO]],COLUMN(),0)</f>
+        <v>2000</v>
+      </c>
+      <c r="D8" s="5">
+        <f>VLOOKUP($H$2,Table24[[#All],[Provider]:[HMO]],COLUMN(),0)</f>
+        <v>4000</v>
+      </c>
+      <c r="E8" s="5">
+        <f>VLOOKUP($H$2,Table24[[#All],[Provider]:[HMO]],COLUMN(),0)</f>
+        <v>0</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="I8" s="12">
+        <v>0.24</v>
+      </c>
+      <c r="K8" t="s">
+        <v>21</v>
+      </c>
+      <c r="L8" t="s">
+        <v>20</v>
+      </c>
+      <c r="M8" t="s">
+        <v>41</v>
+      </c>
+      <c r="N8" t="s">
+        <v>50</v>
+      </c>
+      <c r="O8" t="s">
+        <v>51</v>
+      </c>
+      <c r="P8" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16">
+      <c r="A9" t="s">
+        <v>4</v>
+      </c>
+      <c r="B9" s="5">
         <f>VLOOKUP($H$2,Table4[[#All],[Provider]:[HMO]],COLUMN(),0)</f>
         <v>3000</v>
       </c>
-      <c r="C8" s="5">
+      <c r="C9" s="5">
         <f>VLOOKUP($H$2,Table4[[#All],[Provider]:[HMO]],COLUMN(),0)</f>
         <v>4000</v>
       </c>
-      <c r="D8" s="5">
+      <c r="D9" s="5">
         <f>VLOOKUP($H$2,Table4[[#All],[Provider]:[HMO]],COLUMN(),0)</f>
         <v>7000</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E9" s="5">
         <f>VLOOKUP($H$2,Table4[[#All],[Provider]:[HMO]],COLUMN(),0)</f>
         <v>1500</v>
       </c>
-      <c r="G8" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="I8" s="12">
-        <v>0.24</v>
-      </c>
-      <c r="K8" t="s">
+      <c r="I9" s="12">
+        <v>0.32</v>
+      </c>
+      <c r="K9" t="s">
+        <v>5</v>
+      </c>
+      <c r="L9" t="s">
         <v>22</v>
       </c>
-      <c r="L8" t="s">
-        <v>21</v>
-      </c>
-      <c r="M8" t="s">
-        <v>42</v>
-      </c>
-      <c r="N8" t="s">
-        <v>51</v>
-      </c>
-      <c r="O8" t="s">
-        <v>52</v>
-      </c>
-      <c r="P8" t="s">
+      <c r="M9" s="1">
+        <v>750</v>
+      </c>
+      <c r="N9" s="1">
+        <v>2000</v>
+      </c>
+      <c r="O9" s="1">
+        <v>4000</v>
+      </c>
+      <c r="P9" s="1">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:16">
-      <c r="B9" s="6" t="str">
+    <row r="10" spans="1:16">
+      <c r="B10" s="6" t="str">
         <f>Table1[[#Headers],[PPO]]</f>
         <v>PPO</v>
       </c>
-      <c r="C9" s="6" t="str">
+      <c r="C10" s="6" t="str">
         <f>Table1[[#Headers],[HSA+]]</f>
         <v>HSA+</v>
       </c>
-      <c r="D9" s="6" t="str">
+      <c r="D10" s="6" t="str">
         <f>Table1[[#Headers],[HSAe]]</f>
         <v>HSAe</v>
       </c>
-      <c r="E9" s="6" t="str">
+      <c r="E10" s="6" t="str">
         <f>Table1[[#Headers],[HMO]]</f>
         <v>HMO</v>
       </c>
-      <c r="I9" s="12">
-        <v>0.32</v>
-      </c>
-      <c r="K9" t="s">
-        <v>6</v>
-      </c>
-      <c r="L9" t="s">
-        <v>23</v>
-      </c>
-      <c r="M9" s="1">
-        <v>750</v>
-      </c>
-      <c r="N9" s="1">
-        <v>2000</v>
-      </c>
-      <c r="O9" s="1">
-        <v>4000</v>
-      </c>
-      <c r="P9" s="1">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16">
-      <c r="A10" t="s">
-        <v>7</v>
-      </c>
-      <c r="B10" s="3">
-        <f>SUM(B3:B6)</f>
-        <v>1016.856</v>
-      </c>
-      <c r="C10" s="3">
-        <f>SUM(C3:C6)</f>
-        <v>-559.45399999999995</v>
-      </c>
-      <c r="D10" s="3">
-        <f>SUM(D3:D6)</f>
-        <v>-813.66800000000001</v>
-      </c>
-      <c r="E10" s="3">
-        <f>SUM(E3:E6)</f>
-        <v>920.43</v>
-      </c>
       <c r="I10" s="12">
         <v>0.35</v>
       </c>
       <c r="K10" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M10" s="1">
         <v>1500</v>
@@ -2952,22 +2949,22 @@
     </row>
     <row r="11" spans="1:16">
       <c r="A11" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B11" s="3">
-        <f>SUM(B3:B7)</f>
-        <v>1766.856</v>
+        <f>SUM(B4:B7)</f>
+        <v>1016.856</v>
       </c>
       <c r="C11" s="3">
-        <f>SUM(C3:C7)</f>
-        <v>1440.546</v>
+        <f>SUM(C4:C7)</f>
+        <v>-559.45399999999995</v>
       </c>
       <c r="D11" s="3">
-        <f>SUM(D3:D7)</f>
-        <v>3186.3319999999999</v>
+        <f>SUM(D4:D7)</f>
+        <v>-813.66800000000001</v>
       </c>
       <c r="E11" s="3">
-        <f>SUM(E3:E7)</f>
+        <f>SUM(E4:E7)</f>
         <v>920.43</v>
       </c>
       <c r="I11" s="12">
@@ -2983,72 +2980,72 @@
         <v>8</v>
       </c>
       <c r="B12" s="3">
-        <f>SUM(B3:B6,B8)</f>
+        <f>SUM(B4:B8)</f>
+        <v>1766.856</v>
+      </c>
+      <c r="C12" s="3">
+        <f>SUM(C4:C8)</f>
+        <v>1440.546</v>
+      </c>
+      <c r="D12" s="3">
+        <f>SUM(D4:D8)</f>
+        <v>3186.3319999999999</v>
+      </c>
+      <c r="E12" s="3">
+        <f>SUM(E4:E8)</f>
+        <v>920.43</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16">
+      <c r="A13" t="s">
+        <v>7</v>
+      </c>
+      <c r="B13" s="3">
+        <f>SUM(B4:B7,B9)</f>
         <v>4016.8559999999998</v>
       </c>
-      <c r="C12" s="3">
-        <f>SUM(C3:C6,C8)</f>
+      <c r="C13" s="3">
+        <f>SUM(C4:C7,C9)</f>
         <v>3440.5460000000003</v>
       </c>
-      <c r="D12" s="3">
-        <f>SUM(D3:D6,D8)</f>
+      <c r="D13" s="3">
+        <f>SUM(D4:D7,D9)</f>
         <v>6186.3320000000003</v>
       </c>
-      <c r="E12" s="3">
-        <f>SUM(E3:E6,E8)</f>
+      <c r="E13" s="3">
+        <f>SUM(E4:E7,E9)</f>
         <v>2420.4299999999998</v>
       </c>
-    </row>
-    <row r="13" spans="1:16">
-      <c r="B13" s="5"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
       <c r="K13" s="8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="L13" s="8" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="M13" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="N13" t="s">
+        <v>50</v>
+      </c>
+      <c r="O13" t="s">
         <v>51</v>
-      </c>
-      <c r="O13" t="s">
-        <v>52</v>
       </c>
       <c r="P13" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:16">
-      <c r="A14" t="s">
-        <v>10</v>
-      </c>
-      <c r="B14" s="3">
-        <f>AVERAGE(B10:B12)</f>
-        <v>2266.8559999999998</v>
-      </c>
-      <c r="C14" s="3">
-        <f>AVERAGE(C10:C12)</f>
-        <v>1440.5460000000003</v>
-      </c>
-      <c r="D14" s="3">
-        <f>AVERAGE(D10:D12)</f>
-        <v>2852.9986666666664</v>
-      </c>
-      <c r="E14" s="3">
-        <f>AVERAGE(E10:E12)</f>
-        <v>1420.43</v>
-      </c>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
+      <c r="D14" s="5"/>
+      <c r="E14" s="5"/>
       <c r="J14" s="2"/>
       <c r="K14" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L14" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="M14" s="1">
         <v>3000</v>
@@ -3064,23 +3061,35 @@
       </c>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1">
-      <c r="A15" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
+      <c r="A15" t="s">
+        <v>9</v>
+      </c>
+      <c r="B15" s="3">
+        <f>AVERAGE(B11:B13)</f>
+        <v>2266.8559999999998</v>
+      </c>
+      <c r="C15" s="3">
+        <f>AVERAGE(C11:C13)</f>
+        <v>1440.5460000000003</v>
+      </c>
+      <c r="D15" s="3">
+        <f>AVERAGE(D11:D13)</f>
+        <v>2852.9986666666664</v>
+      </c>
+      <c r="E15" s="3">
+        <f>AVERAGE(E11:E13)</f>
+        <v>1420.43</v>
+      </c>
       <c r="F15" s="2"/>
       <c r="G15" s="2"/>
       <c r="H15" s="2"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L15" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="M15" s="1">
         <v>6000</v>
@@ -3098,35 +3107,44 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="B16" s="15"/>
-      <c r="C16" s="15"/>
-      <c r="D16" s="15"/>
-      <c r="E16" s="15"/>
+        <v>25</v>
+      </c>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
       <c r="M16" s="1"/>
       <c r="N16" s="1"/>
       <c r="O16" s="1"/>
       <c r="P16" s="1"/>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="2"/>
+      <c r="A17" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="B17" s="15"/>
       <c r="C17" s="15"/>
       <c r="D17" s="15"/>
       <c r="E17" s="15"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
+      <c r="A18" s="2"/>
+      <c r="B18" s="15"/>
+      <c r="C18" s="15"/>
+      <c r="D18" s="15"/>
+      <c r="E18" s="15"/>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="B10:E10">
+  <conditionalFormatting sqref="B11:E11">
     <cfRule type="colorScale" priority="7">
       <colorScale>
         <cfvo type="min"/>
@@ -3138,7 +3156,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B11:E11">
+  <conditionalFormatting sqref="B12:E12">
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="min"/>
@@ -3150,7 +3168,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B12:E12">
+  <conditionalFormatting sqref="B13:E13">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -3162,7 +3180,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:E14">
+  <conditionalFormatting sqref="B15:E15">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -3219,7 +3237,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="C1" s="22"/>
       <c r="D1" s="22"/>
@@ -3235,27 +3253,27 @@
     </row>
     <row r="4" spans="1:6">
       <c r="B4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>49</v>
+      </c>
+      <c r="E4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F4" t="s">
         <v>48</v>
-      </c>
-      <c r="D4" t="s">
-        <v>50</v>
-      </c>
-      <c r="E4" t="s">
-        <v>53</v>
-      </c>
-      <c r="F4" t="s">
-        <v>49</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C5" s="18">
         <f t="shared" ref="C5:C9" si="0">C15/D25-1</f>
@@ -3276,10 +3294,10 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C6" s="18">
         <f t="shared" si="0"/>
@@ -3300,10 +3318,10 @@
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C7" s="18">
         <f t="shared" si="0"/>
@@ -3324,10 +3342,10 @@
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C8" s="18">
         <f t="shared" si="0"/>
@@ -3348,10 +3366,10 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" s="18">
         <f t="shared" si="0"/>
@@ -3388,16 +3406,16 @@
     </row>
     <row r="14" spans="1:6">
       <c r="B14" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
+        <v>50</v>
+      </c>
+      <c r="E14" t="s">
         <v>51</v>
-      </c>
-      <c r="E14" t="s">
-        <v>52</v>
       </c>
       <c r="F14" t="s">
         <v>0</v>
@@ -3409,7 +3427,7 @@
         <v>2026A</v>
       </c>
       <c r="B15" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C15" s="1">
         <v>63</v>
@@ -3430,7 +3448,7 @@
         <v>2026B</v>
       </c>
       <c r="B16" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16" s="1">
         <v>116</v>
@@ -3451,7 +3469,7 @@
         <v>2026C</v>
       </c>
       <c r="B17" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C17" s="1">
         <v>197</v>
@@ -3472,7 +3490,7 @@
         <v>2026D</v>
       </c>
       <c r="B18" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C18" s="1">
         <v>278</v>
@@ -3493,7 +3511,7 @@
         <v>2026E</v>
       </c>
       <c r="B19" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C19" s="1">
         <v>434</v>
@@ -3517,14 +3535,14 @@
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
       <c r="I21" s="22" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="J21" s="22"/>
       <c r="K21" s="22"/>
       <c r="L21" s="22"/>
       <c r="M21" s="22"/>
       <c r="N21" s="20" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O21" s="10">
         <v>2025</v>
@@ -3542,7 +3560,7 @@
       <c r="L22" s="22"/>
       <c r="M22" s="22"/>
       <c r="N22" s="20" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="O22" s="10">
         <v>2024</v>
@@ -3550,31 +3568,31 @@
     </row>
     <row r="24" spans="1:15">
       <c r="B24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24" t="s">
         <v>12</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>13</v>
-      </c>
-      <c r="E24" t="s">
-        <v>14</v>
       </c>
       <c r="F24" t="s">
         <v>0</v>
       </c>
       <c r="I24" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="J24" t="s">
+        <v>11</v>
+      </c>
+      <c r="K24" t="s">
         <v>12</v>
       </c>
-      <c r="K24" t="s">
+      <c r="L24" t="s">
         <v>13</v>
-      </c>
-      <c r="L24" t="s">
-        <v>14</v>
       </c>
       <c r="M24" t="s">
         <v>0</v>
@@ -3586,7 +3604,7 @@
         <v>2025A</v>
       </c>
       <c r="B25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C25" s="1">
         <v>294</v>
@@ -3601,25 +3619,25 @@
         <v>122</v>
       </c>
       <c r="H25" s="21" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="I25" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="J25" s="18">
-        <f>VLOOKUP(Year1&amp;$A5,$A$10:$F$1019,COLUMN(C$4),0)/VLOOKUP(Year2&amp;$A5,$A$10:$F$1019,COLUMN(C$4),0)-1</f>
+        <f t="shared" ref="J25:M29" si="4">VLOOKUP(Year1&amp;$A5,$A$10:$F$1019,COLUMN(C$4),0)/VLOOKUP(Year2&amp;$A5,$A$10:$F$1019,COLUMN(C$4),0)-1</f>
         <v>0.11787072243346008</v>
       </c>
       <c r="K25" s="18">
-        <f>VLOOKUP(Year1&amp;$A5,$A$10:$F$1019,COLUMN(D$4),0)/VLOOKUP(Year2&amp;$A5,$A$10:$F$1019,COLUMN(D$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11111111111111116</v>
       </c>
       <c r="L25" s="18">
-        <f>VLOOKUP(Year1&amp;$A5,$A$10:$F$1019,COLUMN(E$4),0)/VLOOKUP(Year2&amp;$A5,$A$10:$F$1019,COLUMN(E$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.10000000000000009</v>
       </c>
       <c r="M25" s="18">
-        <f>VLOOKUP(Year1&amp;$A5,$A$10:$F$1019,COLUMN(F$4),0)/VLOOKUP(Year2&amp;$A5,$A$10:$F$1019,COLUMN(F$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11926605504587151</v>
       </c>
     </row>
@@ -3629,7 +3647,7 @@
         <v>2025B</v>
       </c>
       <c r="B26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C26" s="1">
         <v>350</v>
@@ -3644,25 +3662,25 @@
         <v>160</v>
       </c>
       <c r="H26" s="21" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="I26" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="J26" s="18">
-        <f>VLOOKUP(Year1&amp;$A6,$A$10:$F$1019,COLUMN(C$4),0)/VLOOKUP(Year2&amp;$A6,$A$10:$F$1019,COLUMN(C$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.1182108626198084</v>
       </c>
       <c r="K26" s="18">
-        <f>VLOOKUP(Year1&amp;$A6,$A$10:$F$1019,COLUMN(D$4),0)/VLOOKUP(Year2&amp;$A6,$A$10:$F$1019,COLUMN(D$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.12244897959183665</v>
       </c>
       <c r="L26" s="18">
-        <f>VLOOKUP(Year1&amp;$A6,$A$10:$F$1019,COLUMN(E$4),0)/VLOOKUP(Year2&amp;$A6,$A$10:$F$1019,COLUMN(E$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.12195121951219523</v>
       </c>
       <c r="M26" s="18">
-        <f>VLOOKUP(Year1&amp;$A6,$A$10:$F$1019,COLUMN(F$4),0)/VLOOKUP(Year2&amp;$A6,$A$10:$F$1019,COLUMN(F$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11888111888111896</v>
       </c>
     </row>
@@ -3672,7 +3690,7 @@
         <v>2025C</v>
       </c>
       <c r="B27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C27" s="1">
         <v>421</v>
@@ -3687,25 +3705,25 @@
         <v>208</v>
       </c>
       <c r="H27" s="21" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="I27" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="J27" s="18">
-        <f>VLOOKUP(Year1&amp;$A7,$A$10:$F$1019,COLUMN(C$4),0)/VLOOKUP(Year2&amp;$A7,$A$10:$F$1019,COLUMN(C$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11671087533156488</v>
       </c>
       <c r="K27" s="18">
-        <f>VLOOKUP(Year1&amp;$A7,$A$10:$F$1019,COLUMN(D$4),0)/VLOOKUP(Year2&amp;$A7,$A$10:$F$1019,COLUMN(D$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11538461538461542</v>
       </c>
       <c r="L27" s="18">
-        <f>VLOOKUP(Year1&amp;$A7,$A$10:$F$1019,COLUMN(E$4),0)/VLOOKUP(Year2&amp;$A7,$A$10:$F$1019,COLUMN(E$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11578947368421044</v>
       </c>
       <c r="M27" s="18">
-        <f>VLOOKUP(Year1&amp;$A7,$A$10:$F$1019,COLUMN(F$4),0)/VLOOKUP(Year2&amp;$A7,$A$10:$F$1019,COLUMN(F$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11827956989247301</v>
       </c>
     </row>
@@ -3715,7 +3733,7 @@
         <v>2025D</v>
       </c>
       <c r="B28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C28" s="1">
         <v>516</v>
@@ -3730,25 +3748,25 @@
         <v>264</v>
       </c>
       <c r="H28" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="J28" s="18">
-        <f>VLOOKUP(Year1&amp;$A8,$A$10:$F$1019,COLUMN(C$4),0)/VLOOKUP(Year2&amp;$A8,$A$10:$F$1019,COLUMN(C$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11688311688311681</v>
       </c>
       <c r="K28" s="18">
-        <f>VLOOKUP(Year1&amp;$A8,$A$10:$F$1019,COLUMN(D$4),0)/VLOOKUP(Year2&amp;$A8,$A$10:$F$1019,COLUMN(D$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11790393013100431</v>
       </c>
       <c r="L28" s="18">
-        <f>VLOOKUP(Year1&amp;$A8,$A$10:$F$1019,COLUMN(E$4),0)/VLOOKUP(Year2&amp;$A8,$A$10:$F$1019,COLUMN(E$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.12080536912751683</v>
       </c>
       <c r="M28" s="18">
-        <f>VLOOKUP(Year1&amp;$A8,$A$10:$F$1019,COLUMN(F$4),0)/VLOOKUP(Year2&amp;$A8,$A$10:$F$1019,COLUMN(F$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11864406779661008</v>
       </c>
     </row>
@@ -3758,7 +3776,7 @@
         <v>2025E</v>
       </c>
       <c r="B29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C29" s="1">
         <v>651</v>
@@ -3773,25 +3791,25 @@
         <v>353</v>
       </c>
       <c r="H29" s="21" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J29" s="18">
-        <f>VLOOKUP(Year1&amp;$A9,$A$10:$F$1019,COLUMN(C$4),0)/VLOOKUP(Year2&amp;$A9,$A$10:$F$1019,COLUMN(C$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11663807890222988</v>
       </c>
       <c r="K29" s="18">
-        <f>VLOOKUP(Year1&amp;$A9,$A$10:$F$1019,COLUMN(D$4),0)/VLOOKUP(Year2&amp;$A9,$A$10:$F$1019,COLUMN(D$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11641791044776117</v>
       </c>
       <c r="L29" s="18">
-        <f>VLOOKUP(Year1&amp;$A9,$A$10:$F$1019,COLUMN(E$4),0)/VLOOKUP(Year2&amp;$A9,$A$10:$F$1019,COLUMN(E$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11894273127753308</v>
       </c>
       <c r="M29" s="18">
-        <f>VLOOKUP(Year1&amp;$A9,$A$10:$F$1019,COLUMN(F$4),0)/VLOOKUP(Year2&amp;$A9,$A$10:$F$1019,COLUMN(F$4),0)-1</f>
+        <f t="shared" si="4"/>
         <v>0.11708860759493667</v>
       </c>
     </row>
@@ -3814,16 +3832,16 @@
     </row>
     <row r="34" spans="1:6">
       <c r="B34" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C34" t="s">
+        <v>11</v>
+      </c>
+      <c r="D34" t="s">
         <v>12</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>13</v>
-      </c>
-      <c r="E34" t="s">
-        <v>14</v>
       </c>
       <c r="F34" t="s">
         <v>0</v>
@@ -3835,7 +3853,7 @@
         <v>2024A</v>
       </c>
       <c r="B35" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C35" s="1">
         <v>263</v>
@@ -3856,7 +3874,7 @@
         <v>2024B</v>
       </c>
       <c r="B36" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C36" s="1">
         <v>313</v>
@@ -3877,7 +3895,7 @@
         <v>2024C</v>
       </c>
       <c r="B37" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C37" s="1">
         <v>377</v>
@@ -3898,7 +3916,7 @@
         <v>2024D</v>
       </c>
       <c r="B38" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C38" s="1">
         <v>462</v>
@@ -3919,7 +3937,7 @@
         <v>2024E</v>
       </c>
       <c r="B39" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C39" s="1">
         <v>583</v>
@@ -3961,16 +3979,16 @@
     <row r="44" spans="1:6">
       <c r="A44" s="21"/>
       <c r="B44" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C44" t="s">
+        <v>11</v>
+      </c>
+      <c r="D44" t="s">
         <v>12</v>
       </c>
-      <c r="D44" t="s">
+      <c r="E44" t="s">
         <v>13</v>
-      </c>
-      <c r="E44" t="s">
-        <v>14</v>
       </c>
       <c r="F44" t="s">
         <v>0</v>
@@ -3982,7 +4000,7 @@
         <v>2023A</v>
       </c>
       <c r="B45" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C45" s="1">
         <v>250</v>
@@ -4003,7 +4021,7 @@
         <v>2023B</v>
       </c>
       <c r="B46" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C46" s="1">
         <v>298</v>
@@ -4024,7 +4042,7 @@
         <v>2023C</v>
       </c>
       <c r="B47" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C47" s="1">
         <v>359</v>
@@ -4045,7 +4063,7 @@
         <v>2023D</v>
       </c>
       <c r="B48" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C48" s="1">
         <v>440</v>
@@ -4066,7 +4084,7 @@
         <v>2023E</v>
       </c>
       <c r="B49" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C49" s="1">
         <v>555</v>
@@ -4108,16 +4126,16 @@
     <row r="54" spans="1:6">
       <c r="A54" s="21"/>
       <c r="B54" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D54" t="s">
         <v>12</v>
       </c>
-      <c r="D54" t="s">
+      <c r="E54" t="s">
         <v>13</v>
-      </c>
-      <c r="E54" t="s">
-        <v>14</v>
       </c>
       <c r="F54" t="s">
         <v>0</v>
@@ -4129,7 +4147,7 @@
         <v>2022A</v>
       </c>
       <c r="B55" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C55" s="1">
         <v>240</v>
@@ -4150,7 +4168,7 @@
         <v>2022B</v>
       </c>
       <c r="B56" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C56" s="1">
         <v>284</v>
@@ -4171,7 +4189,7 @@
         <v>2022C</v>
       </c>
       <c r="B57" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C57" s="1">
         <v>342</v>
@@ -4192,7 +4210,7 @@
         <v>2022D</v>
       </c>
       <c r="B58" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C58" s="1">
         <v>415</v>
@@ -4213,7 +4231,7 @@
         <v>2022E</v>
       </c>
       <c r="B59" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C59" s="1">
         <v>524</v>
@@ -4255,16 +4273,16 @@
     <row r="64" spans="1:6">
       <c r="A64" s="21"/>
       <c r="B64" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C64" t="s">
+        <v>11</v>
+      </c>
+      <c r="D64" t="s">
         <v>12</v>
       </c>
-      <c r="D64" t="s">
+      <c r="E64" t="s">
         <v>13</v>
-      </c>
-      <c r="E64" t="s">
-        <v>14</v>
       </c>
       <c r="F64" t="s">
         <v>0</v>
@@ -4276,7 +4294,7 @@
         <v>2021A</v>
       </c>
       <c r="B65" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C65" s="1">
         <v>234</v>
@@ -4297,7 +4315,7 @@
         <v>2021B</v>
       </c>
       <c r="B66" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C66" s="1">
         <v>277</v>
@@ -4318,7 +4336,7 @@
         <v>2021C</v>
       </c>
       <c r="B67" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C67" s="1">
         <v>334</v>
@@ -4339,7 +4357,7 @@
         <v>2021D</v>
       </c>
       <c r="B68" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C68" s="1">
         <v>405</v>
@@ -4360,7 +4378,7 @@
         <v>2021E</v>
       </c>
       <c r="B69" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C69" s="1">
         <v>511</v>
@@ -4402,16 +4420,16 @@
     <row r="74" spans="1:6">
       <c r="A74" s="21"/>
       <c r="B74" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C74" t="s">
+        <v>11</v>
+      </c>
+      <c r="D74" t="s">
         <v>12</v>
       </c>
-      <c r="D74" t="s">
+      <c r="E74" t="s">
         <v>13</v>
-      </c>
-      <c r="E74" t="s">
-        <v>14</v>
       </c>
       <c r="F74" t="s">
         <v>0</v>
@@ -4423,7 +4441,7 @@
         <v>2020A</v>
       </c>
       <c r="B75" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C75" s="1">
         <v>228</v>
@@ -4444,7 +4462,7 @@
         <v>2020B</v>
       </c>
       <c r="B76" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C76" s="1">
         <v>270</v>
@@ -4465,7 +4483,7 @@
         <v>2020C</v>
       </c>
       <c r="B77" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C77" s="1">
         <v>325</v>
@@ -4486,7 +4504,7 @@
         <v>2020D</v>
       </c>
       <c r="B78" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C78" s="1">
         <v>394</v>
@@ -4507,7 +4525,7 @@
         <v>2020E</v>
       </c>
       <c r="B79" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C79" s="1">
         <v>497</v>
@@ -4549,16 +4567,16 @@
     <row r="84" spans="1:6">
       <c r="A84" s="21"/>
       <c r="B84" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C84" t="s">
+        <v>11</v>
+      </c>
+      <c r="D84" t="s">
         <v>12</v>
       </c>
-      <c r="D84" t="s">
+      <c r="E84" t="s">
         <v>13</v>
-      </c>
-      <c r="E84" t="s">
-        <v>14</v>
       </c>
       <c r="F84" t="s">
         <v>0</v>
@@ -4570,7 +4588,7 @@
         <v>2019A</v>
       </c>
       <c r="B85" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C85" s="1">
         <v>217</v>
@@ -4591,7 +4609,7 @@
         <v>2019B</v>
       </c>
       <c r="B86" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C86" s="1">
         <v>257</v>
@@ -4612,7 +4630,7 @@
         <v>2019C</v>
       </c>
       <c r="B87" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C87" s="1">
         <v>310</v>
@@ -4633,7 +4651,7 @@
         <v>2019D</v>
       </c>
       <c r="B88" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C88" s="1">
         <v>376</v>
@@ -4654,7 +4672,7 @@
         <v>2019E</v>
       </c>
       <c r="B89" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C89" s="1">
         <v>474</v>
@@ -4671,16 +4689,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B1:F2"/>
+    <mergeCell ref="B21:F22"/>
+    <mergeCell ref="B51:F52"/>
+    <mergeCell ref="B61:F62"/>
+    <mergeCell ref="B71:F72"/>
     <mergeCell ref="I21:M22"/>
     <mergeCell ref="B81:F82"/>
     <mergeCell ref="B41:F42"/>
     <mergeCell ref="B11:F12"/>
     <mergeCell ref="B31:F32"/>
-    <mergeCell ref="B1:F2"/>
-    <mergeCell ref="B21:F22"/>
-    <mergeCell ref="B51:F52"/>
-    <mergeCell ref="B61:F62"/>
-    <mergeCell ref="B71:F72"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>

--- a/2026 NU health comparison - INDIVIDUAL.xlsx
+++ b/2026 NU health comparison - INDIVIDUAL.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pbh634\Documents\GitHub\nu-health-plan-comparison\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFF0ECCA-6F4A-462B-B8D5-62CAE0FB5929}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF5FD779-1638-480B-8EC7-A7A741928622}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Calculator" sheetId="1" r:id="rId1"/>
@@ -68,7 +68,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="A6" authorId="0" shapeId="0" xr:uid="{537B9FB1-9839-4BC1-B7AA-6E3D4E46E7E0}">
       <text>
         <r>
           <rPr>
@@ -88,7 +88,7 @@
             <charset val="1"/>
           </rPr>
           <t xml:space="preserve">
-NU matches up to $1000 of HSA contributions; this is free money and reduces the yearly cost of care.</t>
+NU matches up to $1000 ($2000 family) of HSA contributions; this is free money and reduces the yearly cost of care.</t>
         </r>
       </text>
     </comment>
@@ -193,7 +193,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="56">
   <si>
     <t>HMO</t>
   </si>
@@ -330,9 +330,6 @@
     <t>Tax savings assumes a reduction in 2026 income taxes due of (2026 Federal tax bracket + 4.95%), where 4.95% is the IL tax rate for 2026.</t>
   </si>
   <si>
-    <t>A FSA tax benefit could be obtained for the PPO plans by contributing to an FSA for the year; however, a FSA is use it or lose it (pre-spending plan) as opposed to a true savings plan.</t>
-  </si>
-  <si>
     <t>% Increase BCBS to UHC</t>
   </si>
   <si>
@@ -361,6 +358,12 @@
   </si>
   <si>
     <t>Monthly HSA</t>
+  </si>
+  <si>
+    <t>In 2026, PPO and HMO plans have a separate prescription drug OOP max. If you expect to need prescription drug coverage, this increases the expected PPO and HMO costs under the deductible scenarios.</t>
+  </si>
+  <si>
+    <t>A FSA tax benefit could be obtained for the PPO or HMO plans by contributing to an FSA for the year; however, a FSA is use it or lose it (pre-spending plan) as opposed to a true savings plan.</t>
   </si>
 </sst>
 </file>
@@ -2568,10 +2571,10 @@
         <v>41</v>
       </c>
       <c r="C1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D1" t="s">
         <v>50</v>
-      </c>
-      <c r="D1" t="s">
-        <v>51</v>
       </c>
       <c r="E1" t="s">
         <v>0</v>
@@ -2592,10 +2595,10 @@
         <v>41</v>
       </c>
       <c r="N1" t="s">
+        <v>49</v>
+      </c>
+      <c r="O1" t="s">
         <v>50</v>
-      </c>
-      <c r="O1" t="s">
-        <v>51</v>
       </c>
       <c r="P1" t="s">
         <v>0</v>
@@ -2603,7 +2606,7 @@
     </row>
     <row r="2" spans="1:16">
       <c r="A2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B2" s="3">
         <f>VLOOKUP($G$2,Table2[#All],COLUMN(),0)</f>
@@ -2648,7 +2651,7 @@
     </row>
     <row r="3" spans="1:16">
       <c r="A3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B3" s="11"/>
       <c r="C3" s="11">
@@ -2856,10 +2859,10 @@
         <v>41</v>
       </c>
       <c r="N8" t="s">
+        <v>49</v>
+      </c>
+      <c r="O8" t="s">
         <v>50</v>
-      </c>
-      <c r="O8" t="s">
-        <v>51</v>
       </c>
       <c r="P8" t="s">
         <v>0</v>
@@ -3026,10 +3029,10 @@
         <v>41</v>
       </c>
       <c r="N13" t="s">
+        <v>49</v>
+      </c>
+      <c r="O13" t="s">
         <v>50</v>
-      </c>
-      <c r="O13" t="s">
-        <v>51</v>
       </c>
       <c r="P13" t="s">
         <v>0</v>
@@ -3128,7 +3131,9 @@
       <c r="E17" s="15"/>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="2"/>
+      <c r="A18" s="2" t="s">
+        <v>55</v>
+      </c>
       <c r="B18" s="15"/>
       <c r="C18" s="15"/>
       <c r="D18" s="15"/>
@@ -3136,7 +3141,7 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="2" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="B19" s="7"/>
       <c r="C19" s="7"/>
@@ -3237,7 +3242,7 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="22" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="C1" s="22"/>
       <c r="D1" s="22"/>
@@ -3256,16 +3261,16 @@
         <v>14</v>
       </c>
       <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>48</v>
+      </c>
+      <c r="E4" t="s">
+        <v>51</v>
+      </c>
+      <c r="F4" t="s">
         <v>47</v>
-      </c>
-      <c r="D4" t="s">
-        <v>49</v>
-      </c>
-      <c r="E4" t="s">
-        <v>52</v>
-      </c>
-      <c r="F4" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -3412,10 +3417,10 @@
         <v>41</v>
       </c>
       <c r="D14" t="s">
+        <v>49</v>
+      </c>
+      <c r="E14" t="s">
         <v>50</v>
-      </c>
-      <c r="E14" t="s">
-        <v>51</v>
       </c>
       <c r="F14" t="s">
         <v>0</v>
@@ -3535,7 +3540,7 @@
       <c r="E21" s="22"/>
       <c r="F21" s="22"/>
       <c r="I21" s="22" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="J21" s="22"/>
       <c r="K21" s="22"/>
@@ -4689,16 +4694,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="I21:M22"/>
+    <mergeCell ref="B81:F82"/>
+    <mergeCell ref="B41:F42"/>
+    <mergeCell ref="B11:F12"/>
+    <mergeCell ref="B31:F32"/>
     <mergeCell ref="B1:F2"/>
     <mergeCell ref="B21:F22"/>
     <mergeCell ref="B51:F52"/>
     <mergeCell ref="B61:F62"/>
     <mergeCell ref="B71:F72"/>
-    <mergeCell ref="I21:M22"/>
-    <mergeCell ref="B81:F82"/>
-    <mergeCell ref="B41:F42"/>
-    <mergeCell ref="B11:F12"/>
-    <mergeCell ref="B31:F32"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
